--- a/SGC-CKN/Excel/d53783b5-951d-43f0-b548-913751e95b9b_Lô_CT-02_PH-77_D800_24-03-2026.xlsx
+++ b/SGC-CKN/Excel/d53783b5-951d-43f0-b548-913751e95b9b_Lô_CT-02_PH-77_D800_24-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
   <si>
     <t>Dự án</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>PH-77</t>
+    <t>P7-77</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>09:45 24/03/2026</t>
+    <t>09:25 24/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -145,20 +145,16 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">00:00
-23/03/2026</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">03:00
 24/03/2026</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+  </si>
+  <si>
     <t xml:space="preserve">06:10
 24/03/2026</t>
   </si>
@@ -196,7 +192,7 @@
     <t>Cuội đa màu sắc TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">09:45
+    <t xml:space="preserve">09:25
 24/03/2026</t>
   </si>
   <si>
@@ -1204,7 +1200,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.27</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.34</v>
@@ -1216,7 +1212,7 @@
         <v>7.34</v>
       </c>
       <c r="J11" s="8">
-        <v>20.35</v>
+        <v>36.7</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1277,7 +1273,7 @@
         <v>-9.49</v>
       </c>
       <c r="G13" s="12">
-        <v>-17.69</v>
+        <v>-17.689999999999998</v>
       </c>
       <c r="H13" s="12">
         <v>0.08</v>
@@ -1309,7 +1305,7 @@
         <v>39</v>
       </c>
       <c r="F14" s="15">
-        <v>-17.69</v>
+        <v>-17.689999999999998</v>
       </c>
       <c r="G14" s="15">
         <v>-21.93</v>
@@ -1347,16 +1343,16 @@
         <v>-21.93</v>
       </c>
       <c r="G15" s="19">
-        <v>-26.06</v>
+        <v>-26.03</v>
       </c>
       <c r="H15" s="19">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="I15" s="19">
-        <v>4.13</v>
-      </c>
-      <c r="J15" s="8">
-        <v>8.26</v>
+        <v>4.1</v>
+      </c>
+      <c r="J15" s="18">
+        <v>1.17</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1373,13 +1369,13 @@
         <v>44</v>
       </c>
       <c r="D16" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="24" t="s">
-        <v>46</v>
-      </c>
       <c r="F16" s="22">
-        <v>-26.06</v>
+        <v>-26.03</v>
       </c>
       <c r="G16" s="22">
         <v>-35.93</v>
@@ -1388,10 +1384,10 @@
         <v>3.17</v>
       </c>
       <c r="I16" s="22">
-        <v>9.87</v>
+        <v>9.9</v>
       </c>
       <c r="J16" s="18">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1399,19 +1395,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="D17" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>48</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>49</v>
       </c>
       <c r="F17" s="25">
         <v>-35.93</v>
@@ -1434,19 +1430,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
+      <c r="D18" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>51</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>52</v>
       </c>
       <c r="F18" s="28">
         <v>-37.5</v>
@@ -1469,19 +1465,19 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="33" t="s">
         <v>53</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>54</v>
       </c>
       <c r="F19" s="31">
         <v>-39.9</v>
@@ -1504,19 +1500,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
+      <c r="D20" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>56</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>57</v>
       </c>
       <c r="F20" s="34">
         <v>-43.1</v>
@@ -1525,13 +1521,13 @@
         <v>-44.65</v>
       </c>
       <c r="H20" s="34">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="I20" s="34">
         <v>1.55</v>
       </c>
       <c r="J20" s="18">
-        <v>1.86</v>
+        <v>3.1</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1539,7 +1535,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1645,31 +1641,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1686,7 +1682,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.27</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.34</v>
@@ -1805,16 +1801,16 @@
         <v>-21.93</v>
       </c>
       <c r="F6" s="19">
-        <v>-26.06</v>
+        <v>-26.03</v>
       </c>
       <c r="G6" s="19">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="H6" s="19">
-        <v>4.13</v>
-      </c>
-      <c r="I6" s="8">
-        <v>8.26</v>
+        <v>4.1</v>
+      </c>
+      <c r="I6" s="18">
+        <v>1.17</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1831,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-26.06</v>
+        <v>-26.03</v>
       </c>
       <c r="F7" s="22">
         <v>-35.93</v>
@@ -1840,10 +1836,10 @@
         <v>3.17</v>
       </c>
       <c r="H7" s="22">
-        <v>9.87</v>
+        <v>9.9</v>
       </c>
       <c r="I7" s="18">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1854,7 +1850,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1883,7 +1879,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1912,7 +1908,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1941,7 +1937,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1953,18 +1949,18 @@
         <v>-44.65</v>
       </c>
       <c r="G11" s="34">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="34">
         <v>1.55</v>
       </c>
       <c r="I11" s="18">
-        <v>1.86</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -1976,19 +1972,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-3.27</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
         <v>-44.65</v>
       </c>
       <c r="G12" s="39">
-        <v>9.75</v>
+        <v>12.42</v>
       </c>
       <c r="H12" s="39">
         <v>44.65</v>
       </c>
       <c r="I12" s="39">
-        <v>4.58</v>
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>
